--- a/out/LSTM-S4_repeat_4_000005.xlsx
+++ b/out/LSTM-S4_repeat_4_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-11.27907012395075</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-11.27907012395075</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4785214654300937</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4785214654300937</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.4785214654300937</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.4785214654300937</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.4785214654300937</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.4785214654300937</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.4785214654300937</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-S4_repeat_4_000005.xlsx
+++ b/out/LSTM-S4_repeat_4_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-11.27907012395075</v>
+        <v>-2.92</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-11.27907012395075</v>
+        <v>-1.919195093615978</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.1214785345699063</v>
+        <v>-0.9183901872319572</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4785214654300937</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4785214654300937</v>
+        <v>0.2824147191520643</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.4785214654300937</v>
+        <v>0.2824147191520643</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.4785214654300937</v>
+        <v>0.2824147191520643</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.4785214654300937</v>
+        <v>0.2824147191520643</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.4785214654300937</v>
+        <v>0.2824147191520643</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.4785214654300937</v>
+        <v>0.2824147191520643</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.2824147191520643</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1214785345699063</v>
+        <v>0.08241471915206423</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-S4_repeat_4_000005.xlsx
+++ b/out/LSTM-S4_repeat_4_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.00172335235401988</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.92</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.0006531677208840847</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.919195093615978</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>1.931609585881233e-05</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9183901872319572</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.0005334774032235146</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.000505292322486639</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0004793680272996426</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.2824147191520643</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0007393946871161461</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.2824147191520643</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0008495352230966091</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.2824147191520643</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0006667627021670341</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.2824147191520643</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0006304867565631866</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.2824147191520643</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0006573889404535294</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.2824147191520643</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0006734570488333702</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.2824147191520643</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0006187031976878643</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0007105092518031597</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.000858343206346035</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001422727946192026</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.001795758958905935</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.002479551825672388</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.002272380050271749</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002467842306941748</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.002132086548954248</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001246596220880747</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.00047641946002841</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.000674285925924778</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0007524029351770878</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001096358988434076</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001510432455688715</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.001541916746646166</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001580751035362482</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001648672390729189</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002695687580853701</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.002369517926126719</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001635680440813303</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0006890366785228252</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0001020855270326138</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.000172165222465992</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0004867748357355595</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0006525558419525623</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.000935959629714489</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001322627533227205</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.001387367490679026</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.001207684632390738</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.16</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0009176689200103283</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0009687556885182858</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.0009837388060986996</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.001017379108816385</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0009886226616799831</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.001059479080140591</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.001205787528306246</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.3</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.001360925380140543</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.001531053800135851</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.001496453303843737</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.001537563744932413</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.001555188093334436</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.001551677007228136</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.00184468412771821</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.001994844991713762</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.001958062406629324</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.001716811675578356</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.001643917057663202</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.001426203642040491</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.001034187152981758</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.0008066147565841675</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0007741870358586311</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.0008398685604333878</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.001077307853847742</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.001325422432273626</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.001515429932624102</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.001585476566106081</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.001620823983103037</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.001377331558614969</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.0009410032071173191</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.002602896187454462</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.002708584535866976</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.003727093804627657</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.003616316709667444</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.003084928262978792</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.002134495880454779</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.001444876659661531</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.001371134538203478</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.001786020118743181</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.002677769865840673</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.16</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.002660681027919054</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.00289369048550725</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.002853888552635908</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.002680405508726835</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.003521260339766741</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.00365125248208642</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.002935178112238646</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.002059470396488905</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.001739958766847849</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.001783826854079962</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.002134597394615412</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.002765292767435312</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.16</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.003413901198655367</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.00356730492785573</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.00342767545953393</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.003092473838478327</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.002872862387448549</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.002887642476707697</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.003519880119711161</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.003511112648993731</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.003494343254715204</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.003809722606092691</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.004148357082158327</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.004022196400910616</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.003989859949797392</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.003616920206695795</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.003429064992815256</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.002982387784868479</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.16</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.003009901847690344</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.16</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.003329739440232515</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.006953323725610971</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.006846650037914515</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.009383976459503174</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.009410630911588669</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.00968288816511631</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.007706401403993368</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.08241471915206423</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.004865572322160006</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.16</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.003011726308614016</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.005458207335323095</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.007402919698506594</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.009597949683666229</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.006946854759007692</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.2300000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.004085366148501635</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.08241471915206423</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>
